--- a/employee_surveys/049_remote_work_experience_feedback_questionnaire--employee_surveys.xlsx
+++ b/employee_surveys/049_remote_work_experience_feedback_questionnaire--employee_surveys.xlsx
@@ -1,15 +1,15 @@
 
 <file path=xl/workbook.xml><?xml version="1.0" encoding="utf-8"?>
-<workbook xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
+<workbook xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
   <workbookPr/>
   <workbookProtection/>
   <bookViews>
     <workbookView visibility="visible" minimized="0" showHorizontalScroll="1" showVerticalScroll="1" showSheetTabs="1" tabRatio="600" firstSheet="0" activeTab="0" autoFilterDateGrouping="1"/>
   </bookViews>
   <sheets>
-    <sheet name="survey" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet name="choices" sheetId="2" state="visible" r:id="rId2"/>
-    <sheet name="settings" sheetId="3" state="visible" r:id="rId3"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="survey" sheetId="1" state="visible" r:id="rId1"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="choices" sheetId="2" state="visible" r:id="rId2"/>
+    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="settings" sheetId="3" state="visible" r:id="rId3"/>
   </sheets>
   <definedNames/>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
@@ -711,8 +711,8 @@
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <cols>
     <col width="50" customWidth="1" min="1" max="1"/>
-    <col width="36" customWidth="1" min="2" max="2"/>
-    <col width="36" customWidth="1" min="3" max="3"/>
+    <col width="23" customWidth="1" min="2" max="2"/>
+    <col width="23" customWidth="1" min="3" max="3"/>
   </cols>
   <sheetData>
     <row r="1">
@@ -740,12 +740,12 @@
       </c>
       <c r="B2" t="inlineStr">
         <is>
-          <t>{'value':_'never'}</t>
+          <t>never</t>
         </is>
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>{'value': 'Never'}</t>
+          <t>Never</t>
         </is>
       </c>
     </row>
@@ -757,12 +757,12 @@
       </c>
       <c r="B3" t="inlineStr">
         <is>
-          <t>{'value':_'rarely'}</t>
+          <t>rarely</t>
         </is>
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>{'value': 'Rarely'}</t>
+          <t>Rarely</t>
         </is>
       </c>
     </row>
@@ -774,12 +774,12 @@
       </c>
       <c r="B4" t="inlineStr">
         <is>
-          <t>{'value':_'occasionally'}</t>
+          <t>occasionally</t>
         </is>
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>{'value': 'Occasionally'}</t>
+          <t>Occasionally</t>
         </is>
       </c>
     </row>
@@ -791,12 +791,12 @@
       </c>
       <c r="B5" t="inlineStr">
         <is>
-          <t>{'value':_'frequently'}</t>
+          <t>frequently</t>
         </is>
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>{'value': 'Frequently'}</t>
+          <t>Frequently</t>
         </is>
       </c>
     </row>
@@ -808,12 +808,12 @@
       </c>
       <c r="B6" t="inlineStr">
         <is>
-          <t>{'value':_'almost_always'}</t>
+          <t>almost_always</t>
         </is>
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>{'value': 'Almost always'}</t>
+          <t>Almost always</t>
         </is>
       </c>
     </row>
@@ -825,12 +825,12 @@
       </c>
       <c r="B7" t="inlineStr">
         <is>
-          <t>{'value':_'very_dissatisfied'}</t>
+          <t>very_dissatisfied</t>
         </is>
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>{'value': 'Very dissatisfied'}</t>
+          <t>Very dissatisfied</t>
         </is>
       </c>
     </row>
@@ -842,12 +842,12 @@
       </c>
       <c r="B8" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_dissatisfied'}</t>
+          <t>somewhat_dissatisfied</t>
         </is>
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat dissatisfied'}</t>
+          <t>Somewhat dissatisfied</t>
         </is>
       </c>
     </row>
@@ -859,12 +859,12 @@
       </c>
       <c r="B9" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -876,12 +876,12 @@
       </c>
       <c r="B10" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_satisfied'}</t>
+          <t>somewhat_satisfied</t>
         </is>
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat satisfied'}</t>
+          <t>Somewhat satisfied</t>
         </is>
       </c>
     </row>
@@ -893,12 +893,12 @@
       </c>
       <c r="B11" t="inlineStr">
         <is>
-          <t>{'value':_'very_satisfied'}</t>
+          <t>very_satisfied</t>
         </is>
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>{'value': 'Very satisfied'}</t>
+          <t>Very satisfied</t>
         </is>
       </c>
     </row>
@@ -910,12 +910,12 @@
       </c>
       <c r="B12" t="inlineStr">
         <is>
-          <t>{'value':_0}</t>
+          <t>0</t>
         </is>
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>{'value': 0}</t>
+          <t>0</t>
         </is>
       </c>
     </row>
@@ -927,12 +927,12 @@
       </c>
       <c r="B13" t="inlineStr">
         <is>
-          <t>{'value':_1}</t>
+          <t>1</t>
         </is>
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>{'value': 1}</t>
+          <t>1</t>
         </is>
       </c>
     </row>
@@ -944,12 +944,12 @@
       </c>
       <c r="B14" t="inlineStr">
         <is>
-          <t>{'value':_2}</t>
+          <t>2</t>
         </is>
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>{'value': 2}</t>
+          <t>2</t>
         </is>
       </c>
     </row>
@@ -961,12 +961,12 @@
       </c>
       <c r="B15" t="inlineStr">
         <is>
-          <t>{'value':_3}</t>
+          <t>3</t>
         </is>
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>{'value': 3}</t>
+          <t>3</t>
         </is>
       </c>
     </row>
@@ -978,12 +978,12 @@
       </c>
       <c r="B16" t="inlineStr">
         <is>
-          <t>{'value':_4}</t>
+          <t>4</t>
         </is>
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>{'value': 4}</t>
+          <t>4</t>
         </is>
       </c>
     </row>
@@ -995,12 +995,12 @@
       </c>
       <c r="B17" t="inlineStr">
         <is>
-          <t>{'value':_5}</t>
+          <t>5</t>
         </is>
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>{'value': 5}</t>
+          <t>5</t>
         </is>
       </c>
     </row>
@@ -1012,12 +1012,12 @@
       </c>
       <c r="B18" t="inlineStr">
         <is>
-          <t>{'value':_6}</t>
+          <t>6</t>
         </is>
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>{'value': 6}</t>
+          <t>6</t>
         </is>
       </c>
     </row>
@@ -1029,12 +1029,12 @@
       </c>
       <c r="B19" t="inlineStr">
         <is>
-          <t>{'value':_7}</t>
+          <t>7</t>
         </is>
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>{'value': 7}</t>
+          <t>7</t>
         </is>
       </c>
     </row>
@@ -1046,12 +1046,12 @@
       </c>
       <c r="B20" t="inlineStr">
         <is>
-          <t>{'value':_8}</t>
+          <t>8</t>
         </is>
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>{'value': 8}</t>
+          <t>8</t>
         </is>
       </c>
     </row>
@@ -1063,12 +1063,12 @@
       </c>
       <c r="B21" t="inlineStr">
         <is>
-          <t>{'value':_9}</t>
+          <t>9</t>
         </is>
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>{'value': 9}</t>
+          <t>9</t>
         </is>
       </c>
     </row>
@@ -1080,12 +1080,12 @@
       </c>
       <c r="B22" t="inlineStr">
         <is>
-          <t>{'value':_10}</t>
+          <t>10</t>
         </is>
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>{'value': 10}</t>
+          <t>10</t>
         </is>
       </c>
     </row>
@@ -1097,12 +1097,12 @@
       </c>
       <c r="B23" t="inlineStr">
         <is>
-          <t>{'value':_11}</t>
+          <t>11</t>
         </is>
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>{'value': 11}</t>
+          <t>11</t>
         </is>
       </c>
     </row>
@@ -1114,12 +1114,12 @@
       </c>
       <c r="B24" t="inlineStr">
         <is>
-          <t>{'value':_12}</t>
+          <t>12</t>
         </is>
       </c>
       <c r="C24" t="inlineStr">
         <is>
-          <t>{'value': 12}</t>
+          <t>12</t>
         </is>
       </c>
     </row>
@@ -1131,12 +1131,12 @@
       </c>
       <c r="B25" t="inlineStr">
         <is>
-          <t>{'value':_13}</t>
+          <t>13</t>
         </is>
       </c>
       <c r="C25" t="inlineStr">
         <is>
-          <t>{'value': 13}</t>
+          <t>13</t>
         </is>
       </c>
     </row>
@@ -1148,12 +1148,12 @@
       </c>
       <c r="B26" t="inlineStr">
         <is>
-          <t>{'value':_14}</t>
+          <t>14</t>
         </is>
       </c>
       <c r="C26" t="inlineStr">
         <is>
-          <t>{'value': 14}</t>
+          <t>14</t>
         </is>
       </c>
     </row>
@@ -1165,12 +1165,12 @@
       </c>
       <c r="B27" t="inlineStr">
         <is>
-          <t>{'value':_15}</t>
+          <t>15</t>
         </is>
       </c>
       <c r="C27" t="inlineStr">
         <is>
-          <t>{'value': 15}</t>
+          <t>15</t>
         </is>
       </c>
     </row>
@@ -1182,12 +1182,12 @@
       </c>
       <c r="B28" t="inlineStr">
         <is>
-          <t>{'value':_16}</t>
+          <t>16</t>
         </is>
       </c>
       <c r="C28" t="inlineStr">
         <is>
-          <t>{'value': 16}</t>
+          <t>16</t>
         </is>
       </c>
     </row>
@@ -1199,12 +1199,12 @@
       </c>
       <c r="B29" t="inlineStr">
         <is>
-          <t>{'value':_17}</t>
+          <t>17</t>
         </is>
       </c>
       <c r="C29" t="inlineStr">
         <is>
-          <t>{'value': 17}</t>
+          <t>17</t>
         </is>
       </c>
     </row>
@@ -1216,12 +1216,12 @@
       </c>
       <c r="B30" t="inlineStr">
         <is>
-          <t>{'value':_18}</t>
+          <t>18</t>
         </is>
       </c>
       <c r="C30" t="inlineStr">
         <is>
-          <t>{'value': 18}</t>
+          <t>18</t>
         </is>
       </c>
     </row>
@@ -1233,12 +1233,12 @@
       </c>
       <c r="B31" t="inlineStr">
         <is>
-          <t>{'value':_19}</t>
+          <t>19</t>
         </is>
       </c>
       <c r="C31" t="inlineStr">
         <is>
-          <t>{'value': 19}</t>
+          <t>19</t>
         </is>
       </c>
     </row>
@@ -1250,12 +1250,12 @@
       </c>
       <c r="B32" t="inlineStr">
         <is>
-          <t>{'value':_20}</t>
+          <t>20</t>
         </is>
       </c>
       <c r="C32" t="inlineStr">
         <is>
-          <t>{'value': 20}</t>
+          <t>20</t>
         </is>
       </c>
     </row>
@@ -1267,12 +1267,12 @@
       </c>
       <c r="B33" t="inlineStr">
         <is>
-          <t>{'value':_21}</t>
+          <t>21</t>
         </is>
       </c>
       <c r="C33" t="inlineStr">
         <is>
-          <t>{'value': 21}</t>
+          <t>21</t>
         </is>
       </c>
     </row>
@@ -1284,12 +1284,12 @@
       </c>
       <c r="B34" t="inlineStr">
         <is>
-          <t>{'value':_22}</t>
+          <t>22</t>
         </is>
       </c>
       <c r="C34" t="inlineStr">
         <is>
-          <t>{'value': 22}</t>
+          <t>22</t>
         </is>
       </c>
     </row>
@@ -1301,12 +1301,12 @@
       </c>
       <c r="B35" t="inlineStr">
         <is>
-          <t>{'value':_23}</t>
+          <t>23</t>
         </is>
       </c>
       <c r="C35" t="inlineStr">
         <is>
-          <t>{'value': 23}</t>
+          <t>23</t>
         </is>
       </c>
     </row>
@@ -1318,12 +1318,12 @@
       </c>
       <c r="B36" t="inlineStr">
         <is>
-          <t>{'value':_24}</t>
+          <t>24</t>
         </is>
       </c>
       <c r="C36" t="inlineStr">
         <is>
-          <t>{'value': 24}</t>
+          <t>24</t>
         </is>
       </c>
     </row>
@@ -1335,12 +1335,12 @@
       </c>
       <c r="B37" t="inlineStr">
         <is>
-          <t>{'value':_25}</t>
+          <t>25</t>
         </is>
       </c>
       <c r="C37" t="inlineStr">
         <is>
-          <t>{'value': 25}</t>
+          <t>25</t>
         </is>
       </c>
     </row>
@@ -1352,12 +1352,12 @@
       </c>
       <c r="B38" t="inlineStr">
         <is>
-          <t>{'value':_26}</t>
+          <t>26</t>
         </is>
       </c>
       <c r="C38" t="inlineStr">
         <is>
-          <t>{'value': 26}</t>
+          <t>26</t>
         </is>
       </c>
     </row>
@@ -1369,12 +1369,12 @@
       </c>
       <c r="B39" t="inlineStr">
         <is>
-          <t>{'value':_27}</t>
+          <t>27</t>
         </is>
       </c>
       <c r="C39" t="inlineStr">
         <is>
-          <t>{'value': 27}</t>
+          <t>27</t>
         </is>
       </c>
     </row>
@@ -1386,12 +1386,12 @@
       </c>
       <c r="B40" t="inlineStr">
         <is>
-          <t>{'value':_28}</t>
+          <t>28</t>
         </is>
       </c>
       <c r="C40" t="inlineStr">
         <is>
-          <t>{'value': 28}</t>
+          <t>28</t>
         </is>
       </c>
     </row>
@@ -1403,12 +1403,12 @@
       </c>
       <c r="B41" t="inlineStr">
         <is>
-          <t>{'value':_29}</t>
+          <t>29</t>
         </is>
       </c>
       <c r="C41" t="inlineStr">
         <is>
-          <t>{'value': 29}</t>
+          <t>29</t>
         </is>
       </c>
     </row>
@@ -1420,12 +1420,12 @@
       </c>
       <c r="B42" t="inlineStr">
         <is>
-          <t>{'value':_30}</t>
+          <t>30</t>
         </is>
       </c>
       <c r="C42" t="inlineStr">
         <is>
-          <t>{'value': 30}</t>
+          <t>30</t>
         </is>
       </c>
     </row>
@@ -1437,12 +1437,12 @@
       </c>
       <c r="B43" t="inlineStr">
         <is>
-          <t>{'value':_'more_than_30'}</t>
+          <t>more_than_30</t>
         </is>
       </c>
       <c r="C43" t="inlineStr">
         <is>
-          <t>{'value': 'More than 30'}</t>
+          <t>More than 30</t>
         </is>
       </c>
     </row>
@@ -1454,12 +1454,12 @@
       </c>
       <c r="B44" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_disagree'}</t>
+          <t>strongly_disagree</t>
         </is>
       </c>
       <c r="C44" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly disagree'}</t>
+          <t>Strongly disagree</t>
         </is>
       </c>
     </row>
@@ -1471,12 +1471,12 @@
       </c>
       <c r="B45" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_disagree'}</t>
+          <t>somewhat_disagree</t>
         </is>
       </c>
       <c r="C45" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat disagree'}</t>
+          <t>Somewhat disagree</t>
         </is>
       </c>
     </row>
@@ -1488,12 +1488,12 @@
       </c>
       <c r="B46" t="inlineStr">
         <is>
-          <t>{'value':_'neutral'}</t>
+          <t>neutral</t>
         </is>
       </c>
       <c r="C46" t="inlineStr">
         <is>
-          <t>{'value': 'Neutral'}</t>
+          <t>Neutral</t>
         </is>
       </c>
     </row>
@@ -1505,12 +1505,12 @@
       </c>
       <c r="B47" t="inlineStr">
         <is>
-          <t>{'value':_'somewhat_agree'}</t>
+          <t>somewhat_agree</t>
         </is>
       </c>
       <c r="C47" t="inlineStr">
         <is>
-          <t>{'value': 'Somewhat agree'}</t>
+          <t>Somewhat agree</t>
         </is>
       </c>
     </row>
@@ -1522,12 +1522,12 @@
       </c>
       <c r="B48" t="inlineStr">
         <is>
-          <t>{'value':_'strongly_agree'}</t>
+          <t>strongly_agree</t>
         </is>
       </c>
       <c r="C48" t="inlineStr">
         <is>
-          <t>{'value': 'Strongly agree'}</t>
+          <t>Strongly agree</t>
         </is>
       </c>
     </row>
